--- a/english.xlsx
+++ b/english.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamit\Desktop\LT\Computational Syntax\lab3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamit\Desktop\LT\Computational Syntax\lab3\Universal-Dependencies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FF1C01-A257-4C41-BF8C-7048A1BC451D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948BCBFF-5538-4D95-857B-5B5F201CE2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
   <si>
     <t>Who</t>
   </si>
@@ -69,6 +69,132 @@
   </si>
   <si>
     <t>punct</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>town</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>two</t>
+  </si>
+  <si>
+    <t>minarets</t>
+  </si>
+  <si>
+    <t>glides</t>
+  </si>
+  <si>
+    <t>by</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>ADJ</t>
+  </si>
+  <si>
+    <t>NOUN</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>NUM</t>
+  </si>
+  <si>
+    <t>VERB</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t>det</t>
+  </si>
+  <si>
+    <t>amod</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>nummod</t>
+  </si>
+  <si>
+    <t>advmod</t>
+  </si>
+  <si>
+    <t>nmod</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>was</t>
+  </si>
+  <si>
+    <t>just</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>boy</t>
+  </si>
+  <si>
+    <t>muddy</t>
+  </si>
+  <si>
+    <t>shoes</t>
+  </si>
+  <si>
+    <t>Shenzhen</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>traffic</t>
+  </si>
+  <si>
+    <t>police</t>
+  </si>
+  <si>
+    <t>have</t>
+  </si>
+  <si>
+    <t>opted</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>unconventional</t>
+  </si>
+  <si>
+    <t>penalties</t>
+  </si>
+  <si>
+    <t>before</t>
+  </si>
+  <si>
+    <t>PROPN</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>cop</t>
   </si>
 </sst>
 </file>
@@ -104,8 +230,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F2D1FC-F999-4D45-A05E-3DEF813FC2A7}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -454,10 +581,10 @@
         <v>1</v>
       </c>
       <c r="D1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -471,10 +598,10 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -488,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -505,10 +632,463 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <f>A6+1</f>
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <f t="shared" ref="A8:A14" si="0">A7+1</f>
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <f>A16+1</f>
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <f t="shared" ref="A18:A24" si="1">A17+1</f>
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <f>A26+1</f>
+        <v>2</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <f t="shared" ref="A28:A36" si="2">A27+1</f>
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/english.xlsx
+++ b/english.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamit\Desktop\LT\Computational Syntax\lab3\Universal-Dependencies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948BCBFF-5538-4D95-857B-5B5F201CE2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12F3BFA-F6A5-4758-84A6-C973C6BB0D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="224">
   <si>
     <t>Who</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Shenzhen</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>traffic</t>
   </si>
   <si>
@@ -195,6 +192,525 @@
   </si>
   <si>
     <t>cop</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>volcanoes</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>called</t>
+  </si>
+  <si>
+    <t>vulcanology</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>sometimes</t>
+  </si>
+  <si>
+    <t>spelled</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>conducted</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>coast</t>
+  </si>
+  <si>
+    <t>Mexican</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>said</t>
+  </si>
+  <si>
+    <t>'s</t>
+  </si>
+  <si>
+    <t>The</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>volcanology</t>
+  </si>
+  <si>
+    <t>witness</t>
+  </si>
+  <si>
+    <t>told</t>
+  </si>
+  <si>
+    <t>that</t>
+  </si>
+  <si>
+    <t>SCONJ</t>
+  </si>
+  <si>
+    <t>victim</t>
+  </si>
+  <si>
+    <t>had</t>
+  </si>
+  <si>
+    <t>attacked</t>
+  </si>
+  <si>
+    <t>suspect</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>most</t>
+  </si>
+  <si>
+    <t>obvious</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>celebrity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>initially</t>
+  </si>
+  <si>
+    <t>quite</t>
+  </si>
+  <si>
+    <t>rare</t>
+  </si>
+  <si>
+    <t>This</t>
+  </si>
+  <si>
+    <t>has</t>
+  </si>
+  <si>
+    <t>not</t>
+  </si>
+  <si>
+    <t>stopped</t>
+  </si>
+  <si>
+    <t>investors</t>
+  </si>
+  <si>
+    <t>flocking</t>
+  </si>
+  <si>
+    <t>put</t>
+  </si>
+  <si>
+    <t>their</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>funds</t>
+  </si>
+  <si>
+    <t>discordance</t>
+  </si>
+  <si>
+    <t>between</t>
+  </si>
+  <si>
+    <t>economic</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>CCONJ</t>
+  </si>
+  <si>
+    <t>political</t>
+  </si>
+  <si>
+    <t>rhetoric</t>
+  </si>
+  <si>
+    <t>familiar</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>should</t>
+  </si>
+  <si>
+    <t>be</t>
+  </si>
+  <si>
+    <t>feasibility</t>
+  </si>
+  <si>
+    <t>estimates</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>would</t>
+  </si>
+  <si>
+    <t>take</t>
+  </si>
+  <si>
+    <t>passengers</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>four</t>
+  </si>
+  <si>
+    <t>minutes</t>
+  </si>
+  <si>
+    <t>cross</t>
+  </si>
+  <si>
+    <t>Potomac</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>gondola</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>collected</t>
+  </si>
+  <si>
+    <t>cards</t>
+  </si>
+  <si>
+    <t>traded</t>
+  </si>
+  <si>
+    <t>them</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>boys</t>
+  </si>
+  <si>
+    <t>this</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>carries</t>
+  </si>
+  <si>
+    <t>penalty</t>
+  </si>
+  <si>
+    <t>five</t>
+  </si>
+  <si>
+    <t>years</t>
+  </si>
+  <si>
+    <t>prison</t>
+  </si>
+  <si>
+    <t>news</t>
+  </si>
+  <si>
+    <t>carried</t>
+  </si>
+  <si>
+    <t>every</t>
+  </si>
+  <si>
+    <t>village</t>
+  </si>
+  <si>
+    <t>province</t>
+  </si>
+  <si>
+    <t>carry</t>
+  </si>
+  <si>
+    <t>these</t>
+  </si>
+  <si>
+    <t>thoughts</t>
+  </si>
+  <si>
+    <t>back</t>
+  </si>
+  <si>
+    <t>my</t>
+  </si>
+  <si>
+    <t>head</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>been</t>
+  </si>
+  <si>
+    <t>over</t>
+  </si>
+  <si>
+    <t>into</t>
+  </si>
+  <si>
+    <t>life</t>
+  </si>
+  <si>
+    <t>eternal</t>
+  </si>
+  <si>
+    <t>casings</t>
+  </si>
+  <si>
+    <t>rotted</t>
+  </si>
+  <si>
+    <t>away</t>
+  </si>
+  <si>
+    <t>replaced</t>
+  </si>
+  <si>
+    <t>she</t>
+  </si>
+  <si>
+    <t>incensed</t>
+  </si>
+  <si>
+    <t>chit</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>dare</t>
+  </si>
+  <si>
+    <t>make</t>
+  </si>
+  <si>
+    <t>fool</t>
+  </si>
+  <si>
+    <t>her</t>
+  </si>
+  <si>
+    <t>front</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>landslide</t>
+  </si>
+  <si>
+    <t>electoral</t>
+  </si>
+  <si>
+    <t>college</t>
+  </si>
+  <si>
+    <t>obscured</t>
+  </si>
+  <si>
+    <t>narrowness</t>
+  </si>
+  <si>
+    <t>victory</t>
+  </si>
+  <si>
+    <t>based</t>
+  </si>
+  <si>
+    <t>popular</t>
+  </si>
+  <si>
+    <t>vote</t>
+  </si>
+  <si>
+    <t>United</t>
+  </si>
+  <si>
+    <t>States</t>
+  </si>
+  <si>
+    <t>troops</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>atropine</t>
+  </si>
+  <si>
+    <t>autoinjectors</t>
+  </si>
+  <si>
+    <t>first-aid</t>
+  </si>
+  <si>
+    <t>kits</t>
+  </si>
+  <si>
+    <t>use</t>
+  </si>
+  <si>
+    <t>organophosphate</t>
+  </si>
+  <si>
+    <t>nerve</t>
+  </si>
+  <si>
+    <t>agent</t>
+  </si>
+  <si>
+    <t>poisoning</t>
+  </si>
+  <si>
+    <t>may</t>
+  </si>
+  <si>
+    <t>accomplish</t>
+  </si>
+  <si>
+    <t>craft</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>cannot</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>force</t>
+  </si>
+  <si>
+    <t>violence</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>only</t>
+  </si>
+  <si>
+    <t>hierarchical</t>
+  </si>
+  <si>
+    <t>society</t>
+  </si>
+  <si>
+    <t>leisure</t>
+  </si>
+  <si>
+    <t>at</t>
+  </si>
+  <si>
+    <t>top</t>
+  </si>
+  <si>
+    <t>can</t>
+  </si>
+  <si>
+    <t>produce</t>
+  </si>
+  <si>
+    <t>works</t>
+  </si>
+  <si>
+    <t>art</t>
+  </si>
+  <si>
+    <t>his</t>
+  </si>
+  <si>
+    <t>ingenuous</t>
+  </si>
+  <si>
+    <t>explanation</t>
+  </si>
+  <si>
+    <t>burned</t>
+  </si>
+  <si>
+    <t>church</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>thought</t>
+  </si>
+  <si>
+    <t>bishop</t>
   </si>
 </sst>
 </file>
@@ -232,7 +748,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F2D1FC-F999-4D45-A05E-3DEF813FC2A7}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E346"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -601,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -657,7 +1173,6 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
-        <f>A6+1</f>
         <v>2</v>
       </c>
       <c r="B7" t="s">
@@ -675,7 +1190,6 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
-        <f t="shared" ref="A8:A14" si="0">A7+1</f>
         <v>3</v>
       </c>
       <c r="B8" t="s">
@@ -693,7 +1207,6 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B9" t="s">
@@ -711,7 +1224,6 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B10" t="s">
@@ -729,7 +1241,6 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B11" t="s">
@@ -747,7 +1258,6 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B12" t="s">
@@ -765,7 +1275,6 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B13" t="s">
@@ -783,7 +1292,6 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B14" t="s">
@@ -818,7 +1326,6 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
-        <f>A16+1</f>
         <v>2</v>
       </c>
       <c r="B17" t="s">
@@ -831,12 +1338,11 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
-        <f t="shared" ref="A18:A24" si="1">A17+1</f>
         <v>3</v>
       </c>
       <c r="B18" t="s">
@@ -854,7 +1360,6 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
-        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B19" t="s">
@@ -872,7 +1377,6 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
-        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B20" t="s">
@@ -890,7 +1394,6 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
-        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B21" t="s">
@@ -908,7 +1411,6 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
-        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B22" t="s">
@@ -926,7 +1428,6 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
-        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B23" t="s">
@@ -944,7 +1445,6 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
-        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B24" t="s">
@@ -968,28 +1468,26 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
-        <f>A26+1</f>
         <v>2</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>40</v>
+      <c r="B27" t="s">
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
-        <f t="shared" ref="A28:A36" si="2">A27+1</f>
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
@@ -997,11 +1495,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -1009,11 +1506,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
-        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -1021,11 +1517,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
-        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
@@ -1033,11 +1528,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>22</v>
@@ -1045,11 +1539,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
@@ -1057,11 +1550,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
-        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
         <v>21</v>
@@ -1069,11 +1561,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
-        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
@@ -1081,7 +1572,6 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
-        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B36" t="s">
@@ -1089,6 +1579,2772 @@
       </c>
       <c r="C36" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>9</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>62</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>8</v>
+      </c>
+      <c r="B72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>13</v>
+      </c>
+      <c r="B77" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>1</v>
+      </c>
+      <c r="B80" t="s">
+        <v>59</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>70</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>3</v>
+      </c>
+      <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>4</v>
+      </c>
+      <c r="B83" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>7</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>8</v>
+      </c>
+      <c r="B87" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>9</v>
+      </c>
+      <c r="B88" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>10</v>
+      </c>
+      <c r="B89" t="s">
+        <v>53</v>
+      </c>
+      <c r="C89" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>11</v>
+      </c>
+      <c r="B90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>13</v>
+      </c>
+      <c r="B92" t="s">
+        <v>90</v>
+      </c>
+      <c r="C92" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>14</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>92</v>
+      </c>
+      <c r="C96" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>3</v>
+      </c>
+      <c r="B97" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>4</v>
+      </c>
+      <c r="B98" t="s">
+        <v>94</v>
+      </c>
+      <c r="C98" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>95</v>
+      </c>
+      <c r="C99" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>96</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>97</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>9</v>
+      </c>
+      <c r="B103" t="s">
+        <v>98</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>10</v>
+      </c>
+      <c r="B104" t="s">
+        <v>99</v>
+      </c>
+      <c r="C104" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>11</v>
+      </c>
+      <c r="B105" t="s">
+        <v>82</v>
+      </c>
+      <c r="C105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>12</v>
+      </c>
+      <c r="B106" t="s">
+        <v>62</v>
+      </c>
+      <c r="C106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>13</v>
+      </c>
+      <c r="B107" t="s">
+        <v>100</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>14</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>91</v>
+      </c>
+      <c r="C110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>2</v>
+      </c>
+      <c r="B111" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>3</v>
+      </c>
+      <c r="B112" t="s">
+        <v>102</v>
+      </c>
+      <c r="C112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>4</v>
+      </c>
+      <c r="B113" t="s">
+        <v>103</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>104</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>6</v>
+      </c>
+      <c r="B115" t="s">
+        <v>105</v>
+      </c>
+      <c r="C115" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>107</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
+        <v>108</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>9</v>
+      </c>
+      <c r="B118" t="s">
+        <v>53</v>
+      </c>
+      <c r="C118" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>10</v>
+      </c>
+      <c r="B119" t="s">
+        <v>109</v>
+      </c>
+      <c r="C119" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>11</v>
+      </c>
+      <c r="B120" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>12</v>
+      </c>
+      <c r="B121" t="s">
+        <v>110</v>
+      </c>
+      <c r="C121" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>13</v>
+      </c>
+      <c r="B122" t="s">
+        <v>111</v>
+      </c>
+      <c r="C122" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>14</v>
+      </c>
+      <c r="B123" t="s">
+        <v>112</v>
+      </c>
+      <c r="C123" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>71</v>
+      </c>
+      <c r="C126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>113</v>
+      </c>
+      <c r="C127" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>3</v>
+      </c>
+      <c r="B128" t="s">
+        <v>51</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" t="s">
+        <v>114</v>
+      </c>
+      <c r="C129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>76</v>
+      </c>
+      <c r="C130" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>6</v>
+      </c>
+      <c r="B131" t="s">
+        <v>115</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>116</v>
+      </c>
+      <c r="C132" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>8</v>
+      </c>
+      <c r="B133" t="s">
+        <v>117</v>
+      </c>
+      <c r="C133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>9</v>
+      </c>
+      <c r="B134" t="s">
+        <v>118</v>
+      </c>
+      <c r="C134" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>10</v>
+      </c>
+      <c r="B135" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>11</v>
+      </c>
+      <c r="B136" t="s">
+        <v>120</v>
+      </c>
+      <c r="C136" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>121</v>
+      </c>
+      <c r="C137" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>13</v>
+      </c>
+      <c r="B138" t="s">
+        <v>67</v>
+      </c>
+      <c r="C138" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>14</v>
+      </c>
+      <c r="B139" t="s">
+        <v>122</v>
+      </c>
+      <c r="C139" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>62</v>
+      </c>
+      <c r="C140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>16</v>
+      </c>
+      <c r="B141" t="s">
+        <v>123</v>
+      </c>
+      <c r="C141" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>17</v>
+      </c>
+      <c r="B142" t="s">
+        <v>124</v>
+      </c>
+      <c r="C142" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>18</v>
+      </c>
+      <c r="B143" t="s">
+        <v>125</v>
+      </c>
+      <c r="C143" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>19</v>
+      </c>
+      <c r="B144" t="s">
+        <v>62</v>
+      </c>
+      <c r="C144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>20</v>
+      </c>
+      <c r="B145" t="s">
+        <v>126</v>
+      </c>
+      <c r="C145" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>21</v>
+      </c>
+      <c r="B146" t="s">
+        <v>18</v>
+      </c>
+      <c r="C146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>127</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>3</v>
+      </c>
+      <c r="B150" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>5</v>
+      </c>
+      <c r="B152" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>6</v>
+      </c>
+      <c r="B153" t="s">
+        <v>131</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>7</v>
+      </c>
+      <c r="B154" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>62</v>
+      </c>
+      <c r="C155" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>9</v>
+      </c>
+      <c r="B156" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>10</v>
+      </c>
+      <c r="B157" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>134</v>
+      </c>
+      <c r="C159" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>3</v>
+      </c>
+      <c r="B161" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>4</v>
+      </c>
+      <c r="B162" t="s">
+        <v>35</v>
+      </c>
+      <c r="C162" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>5</v>
+      </c>
+      <c r="B163" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>6</v>
+      </c>
+      <c r="B164" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>7</v>
+      </c>
+      <c r="B165" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>8</v>
+      </c>
+      <c r="B166" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>9</v>
+      </c>
+      <c r="B167" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>10</v>
+      </c>
+      <c r="B168" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>62</v>
+      </c>
+      <c r="C170" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>2</v>
+      </c>
+      <c r="B171" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>3</v>
+      </c>
+      <c r="B172" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>4</v>
+      </c>
+      <c r="B173" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>5</v>
+      </c>
+      <c r="B174" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>6</v>
+      </c>
+      <c r="B175" t="s">
+        <v>143</v>
+      </c>
+      <c r="C175" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>7</v>
+      </c>
+      <c r="B176" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
+        <v>62</v>
+      </c>
+      <c r="C178" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>10</v>
+      </c>
+      <c r="B179" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>1</v>
+      </c>
+      <c r="B181" t="s">
+        <v>32</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>2</v>
+      </c>
+      <c r="B182" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>3</v>
+      </c>
+      <c r="B183" t="s">
+        <v>147</v>
+      </c>
+      <c r="C183" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>4</v>
+      </c>
+      <c r="B184" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>5</v>
+      </c>
+      <c r="B185" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>6</v>
+      </c>
+      <c r="B186" t="s">
+        <v>62</v>
+      </c>
+      <c r="C186" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>7</v>
+      </c>
+      <c r="B187" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>9</v>
+      </c>
+      <c r="B189" t="s">
+        <v>150</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>10</v>
+      </c>
+      <c r="B190" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>1</v>
+      </c>
+      <c r="B192" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>2</v>
+      </c>
+      <c r="B193" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>3</v>
+      </c>
+      <c r="B194" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>4</v>
+      </c>
+      <c r="B195" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>5</v>
+      </c>
+      <c r="B196" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>6</v>
+      </c>
+      <c r="B197" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>7</v>
+      </c>
+      <c r="B198" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>8</v>
+      </c>
+      <c r="B199" t="s">
+        <v>62</v>
+      </c>
+      <c r="C199" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>9</v>
+      </c>
+      <c r="B200" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <v>10</v>
+      </c>
+      <c r="B201" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <v>1</v>
+      </c>
+      <c r="B203" t="s">
+        <v>62</v>
+      </c>
+      <c r="C203" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <v>2</v>
+      </c>
+      <c r="B204" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <v>3</v>
+      </c>
+      <c r="B205" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206">
+        <v>4</v>
+      </c>
+      <c r="B206" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207">
+        <v>5</v>
+      </c>
+      <c r="B207" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208">
+        <v>6</v>
+      </c>
+      <c r="B208" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209">
+        <v>7</v>
+      </c>
+      <c r="B209" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>8</v>
+      </c>
+      <c r="B210" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>9</v>
+      </c>
+      <c r="B211" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>10</v>
+      </c>
+      <c r="B212" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <v>1</v>
+      </c>
+      <c r="B214" t="s">
+        <v>162</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <v>2</v>
+      </c>
+      <c r="B215" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>3</v>
+      </c>
+      <c r="B216" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>4</v>
+      </c>
+      <c r="B217" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>5</v>
+      </c>
+      <c r="B218" t="s">
+        <v>134</v>
+      </c>
+      <c r="C218" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <v>6</v>
+      </c>
+      <c r="B219" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <v>7</v>
+      </c>
+      <c r="B220" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <v>8</v>
+      </c>
+      <c r="B221" t="s">
+        <v>35</v>
+      </c>
+      <c r="C221" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <v>9</v>
+      </c>
+      <c r="B222" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>10</v>
+      </c>
+      <c r="B223" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <v>11</v>
+      </c>
+      <c r="B224" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <v>12</v>
+      </c>
+      <c r="B225" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <v>13</v>
+      </c>
+      <c r="B226" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <v>14</v>
+      </c>
+      <c r="B227" t="s">
+        <v>35</v>
+      </c>
+      <c r="C227" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <v>15</v>
+      </c>
+      <c r="B228" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>16</v>
+      </c>
+      <c r="B229" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>17</v>
+      </c>
+      <c r="B230" t="s">
+        <v>169</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>18</v>
+      </c>
+      <c r="B231" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <v>19</v>
+      </c>
+      <c r="B232" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233">
+        <v>20</v>
+      </c>
+      <c r="B233" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234">
+        <v>21</v>
+      </c>
+      <c r="B234" t="s">
+        <v>62</v>
+      </c>
+      <c r="C234" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235">
+        <v>22</v>
+      </c>
+      <c r="B235" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237">
+        <v>1</v>
+      </c>
+      <c r="B237" t="s">
+        <v>62</v>
+      </c>
+      <c r="C237" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238">
+        <v>2</v>
+      </c>
+      <c r="B238" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239">
+        <v>3</v>
+      </c>
+      <c r="B239" t="s">
+        <v>127</v>
+      </c>
+      <c r="C239" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240">
+        <v>4</v>
+      </c>
+      <c r="B240" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241">
+        <v>5</v>
+      </c>
+      <c r="B241" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242">
+        <v>6</v>
+      </c>
+      <c r="B242" t="s">
+        <v>62</v>
+      </c>
+      <c r="C242" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243">
+        <v>7</v>
+      </c>
+      <c r="B243" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244">
+        <v>8</v>
+      </c>
+      <c r="B244" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245">
+        <v>9</v>
+      </c>
+      <c r="B245" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246">
+        <v>10</v>
+      </c>
+      <c r="B246" t="s">
+        <v>62</v>
+      </c>
+      <c r="C246" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247">
+        <v>11</v>
+      </c>
+      <c r="B247" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248">
+        <v>12</v>
+      </c>
+      <c r="B248" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249">
+        <v>13</v>
+      </c>
+      <c r="B249" t="s">
+        <v>35</v>
+      </c>
+      <c r="C249" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250">
+        <v>14</v>
+      </c>
+      <c r="B250" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251">
+        <v>15</v>
+      </c>
+      <c r="B251" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252">
+        <v>16</v>
+      </c>
+      <c r="B252" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253">
+        <v>17</v>
+      </c>
+      <c r="B253" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254">
+        <v>18</v>
+      </c>
+      <c r="B254" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255">
+        <v>19</v>
+      </c>
+      <c r="B255" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>20</v>
+      </c>
+      <c r="B256" t="s">
+        <v>62</v>
+      </c>
+      <c r="C256" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257">
+        <v>21</v>
+      </c>
+      <c r="B257" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258">
+        <v>22</v>
+      </c>
+      <c r="B258" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260">
+        <v>1</v>
+      </c>
+      <c r="B260" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261">
+        <v>2</v>
+      </c>
+      <c r="B261" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262">
+        <v>3</v>
+      </c>
+      <c r="B262" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263">
+        <v>4</v>
+      </c>
+      <c r="B263" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264">
+        <v>5</v>
+      </c>
+      <c r="B264" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265">
+        <v>6</v>
+      </c>
+      <c r="B265" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266">
+        <v>7</v>
+      </c>
+      <c r="B266" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A267">
+        <v>8</v>
+      </c>
+      <c r="B267" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A268">
+        <v>9</v>
+      </c>
+      <c r="B268" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A269">
+        <v>10</v>
+      </c>
+      <c r="B269" t="s">
+        <v>98</v>
+      </c>
+      <c r="C269" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A270">
+        <v>11</v>
+      </c>
+      <c r="B270" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A271">
+        <v>12</v>
+      </c>
+      <c r="B271" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A272">
+        <v>13</v>
+      </c>
+      <c r="B272" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A273">
+        <v>14</v>
+      </c>
+      <c r="B273" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274">
+        <v>15</v>
+      </c>
+      <c r="B274" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275">
+        <v>16</v>
+      </c>
+      <c r="B275" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276">
+        <v>17</v>
+      </c>
+      <c r="B276" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277">
+        <v>18</v>
+      </c>
+      <c r="B277" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278">
+        <v>19</v>
+      </c>
+      <c r="B278" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279">
+        <v>20</v>
+      </c>
+      <c r="B279" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280">
+        <v>21</v>
+      </c>
+      <c r="B280" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282">
+        <v>1</v>
+      </c>
+      <c r="B282" t="s">
+        <v>127</v>
+      </c>
+      <c r="C282" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283">
+        <v>2</v>
+      </c>
+      <c r="B283" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284">
+        <v>3</v>
+      </c>
+      <c r="B284" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285">
+        <v>4</v>
+      </c>
+      <c r="B285" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286">
+        <v>5</v>
+      </c>
+      <c r="B286" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287">
+        <v>6</v>
+      </c>
+      <c r="B287" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288">
+        <v>7</v>
+      </c>
+      <c r="B288" t="s">
+        <v>62</v>
+      </c>
+      <c r="C288" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289">
+        <v>8</v>
+      </c>
+      <c r="B289" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290">
+        <v>9</v>
+      </c>
+      <c r="B290" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291">
+        <v>10</v>
+      </c>
+      <c r="B291" t="s">
+        <v>199</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292">
+        <v>11</v>
+      </c>
+      <c r="B292" t="s">
+        <v>127</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293">
+        <v>12</v>
+      </c>
+      <c r="B293" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294">
+        <v>13</v>
+      </c>
+      <c r="B294" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295">
+        <v>14</v>
+      </c>
+      <c r="B295" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296">
+        <v>15</v>
+      </c>
+      <c r="B296" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297">
+        <v>16</v>
+      </c>
+      <c r="B297" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298">
+        <v>17</v>
+      </c>
+      <c r="B298" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299">
+        <v>18</v>
+      </c>
+      <c r="B299" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300">
+        <v>19</v>
+      </c>
+      <c r="B300" t="s">
+        <v>62</v>
+      </c>
+      <c r="C300" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301">
+        <v>20</v>
+      </c>
+      <c r="B301" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302">
+        <v>21</v>
+      </c>
+      <c r="B302" t="s">
+        <v>205</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304">
+        <v>1</v>
+      </c>
+      <c r="B304" t="s">
+        <v>115</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305">
+        <v>2</v>
+      </c>
+      <c r="B305" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306">
+        <v>3</v>
+      </c>
+      <c r="B306" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307">
+        <v>4</v>
+      </c>
+      <c r="B307" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308">
+        <v>5</v>
+      </c>
+      <c r="B308" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309">
+        <v>6</v>
+      </c>
+      <c r="B309" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310">
+        <v>7</v>
+      </c>
+      <c r="B310" t="s">
+        <v>35</v>
+      </c>
+      <c r="C310" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311">
+        <v>8</v>
+      </c>
+      <c r="B311" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312">
+        <v>9</v>
+      </c>
+      <c r="B312" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313">
+        <v>10</v>
+      </c>
+      <c r="B313" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314">
+        <v>11</v>
+      </c>
+      <c r="B314" t="s">
+        <v>35</v>
+      </c>
+      <c r="C314" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315">
+        <v>12</v>
+      </c>
+      <c r="B315" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316">
+        <v>13</v>
+      </c>
+      <c r="B316" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317">
+        <v>14</v>
+      </c>
+      <c r="B317" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318">
+        <v>15</v>
+      </c>
+      <c r="B318" t="s">
+        <v>62</v>
+      </c>
+      <c r="C318" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319">
+        <v>16</v>
+      </c>
+      <c r="B319" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320">
+        <v>17</v>
+      </c>
+      <c r="B320" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321">
+        <v>18</v>
+      </c>
+      <c r="B321" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A322">
+        <v>19</v>
+      </c>
+      <c r="B322" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A323">
+        <v>20</v>
+      </c>
+      <c r="B323" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A324">
+        <v>21</v>
+      </c>
+      <c r="B324" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A326">
+        <v>1</v>
+      </c>
+      <c r="B326" t="s">
+        <v>216</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A327">
+        <v>2</v>
+      </c>
+      <c r="B327" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A328">
+        <v>3</v>
+      </c>
+      <c r="B328" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A329">
+        <v>4</v>
+      </c>
+      <c r="B329" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A330">
+        <v>5</v>
+      </c>
+      <c r="B330" t="s">
+        <v>127</v>
+      </c>
+      <c r="C330" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A331">
+        <v>6</v>
+      </c>
+      <c r="B331" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A332">
+        <v>7</v>
+      </c>
+      <c r="B332" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A333">
+        <v>8</v>
+      </c>
+      <c r="B333" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A334">
+        <v>9</v>
+      </c>
+      <c r="B334" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A335">
+        <v>10</v>
+      </c>
+      <c r="B335" t="s">
+        <v>62</v>
+      </c>
+      <c r="C335" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A336">
+        <v>11</v>
+      </c>
+      <c r="B336" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A337">
+        <v>12</v>
+      </c>
+      <c r="B337" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A338">
+        <v>13</v>
+      </c>
+      <c r="B338" t="s">
+        <v>127</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A339">
+        <v>14</v>
+      </c>
+      <c r="B339" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A340">
+        <v>15</v>
+      </c>
+      <c r="B340" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A341">
+        <v>16</v>
+      </c>
+      <c r="B341" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A342">
+        <v>17</v>
+      </c>
+      <c r="B342" t="s">
+        <v>62</v>
+      </c>
+      <c r="C342" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A343">
+        <v>18</v>
+      </c>
+      <c r="B343" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A344">
+        <v>19</v>
+      </c>
+      <c r="B344" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A345">
+        <v>20</v>
+      </c>
+      <c r="B345" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A346">
+        <v>21</v>
+      </c>
+      <c r="B346" t="s">
+        <v>115</v>
+      </c>
+      <c r="C346" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/english.xlsx
+++ b/english.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamit\Desktop\LT\Computational Syntax\lab3\Universal-Dependencies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12F3BFA-F6A5-4758-84A6-C973C6BB0D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C779657-CD2C-40AD-8F43-47A38DD1CB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="186">
   <si>
     <t>Who</t>
   </si>
@@ -248,9 +248,6 @@
     <t>June</t>
   </si>
   <si>
-    <t>said</t>
-  </si>
-  <si>
     <t>'s</t>
   </si>
   <si>
@@ -584,133 +581,22 @@
     <t>vote</t>
   </si>
   <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>States</t>
-  </si>
-  <si>
-    <t>troops</t>
-  </si>
-  <si>
-    <t>now</t>
-  </si>
-  <si>
-    <t>atropine</t>
-  </si>
-  <si>
-    <t>autoinjectors</t>
-  </si>
-  <si>
-    <t>first-aid</t>
-  </si>
-  <si>
-    <t>kits</t>
-  </si>
-  <si>
-    <t>use</t>
-  </si>
-  <si>
-    <t>organophosphate</t>
-  </si>
-  <si>
-    <t>nerve</t>
-  </si>
-  <si>
-    <t>agent</t>
-  </si>
-  <si>
-    <t>poisoning</t>
-  </si>
-  <si>
-    <t>may</t>
-  </si>
-  <si>
-    <t>accomplish</t>
-  </si>
-  <si>
-    <t>craft</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>run</t>
-  </si>
-  <si>
-    <t>what</t>
-  </si>
-  <si>
-    <t>cannot</t>
-  </si>
-  <si>
-    <t>do</t>
-  </si>
-  <si>
-    <t>force</t>
-  </si>
-  <si>
-    <t>violence</t>
-  </si>
-  <si>
-    <t>short</t>
-  </si>
-  <si>
-    <t>one</t>
-  </si>
-  <si>
-    <t>only</t>
-  </si>
-  <si>
-    <t>hierarchical</t>
-  </si>
-  <si>
-    <t>society</t>
-  </si>
-  <si>
-    <t>leisure</t>
-  </si>
-  <si>
-    <t>at</t>
-  </si>
-  <si>
-    <t>top</t>
-  </si>
-  <si>
-    <t>can</t>
-  </si>
-  <si>
-    <t>produce</t>
-  </si>
-  <si>
-    <t>works</t>
-  </si>
-  <si>
-    <t>art</t>
-  </si>
-  <si>
-    <t>his</t>
-  </si>
-  <si>
-    <t>ingenuous</t>
-  </si>
-  <si>
-    <t>explanation</t>
-  </si>
-  <si>
-    <t>burned</t>
-  </si>
-  <si>
-    <t>church</t>
-  </si>
-  <si>
-    <t>if</t>
-  </si>
-  <si>
-    <t>thought</t>
-  </si>
-  <si>
-    <t>bishop</t>
+    <t>In</t>
+  </si>
+  <si>
+    <t>particular</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">my </t>
+  </si>
+  <si>
+    <t>dramatically</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F2D1FC-F999-4D45-A05E-3DEF813FC2A7}">
-  <dimension ref="A1:E346"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1476,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>49</v>
@@ -1586,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
@@ -1608,7 +1494,7 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
         <v>22</v>
@@ -1652,7 +1538,7 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
         <v>21</v>
@@ -1872,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
         <v>21</v>
@@ -1883,7 +1769,7 @@
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
@@ -1905,10 +1791,10 @@
         <v>5</v>
       </c>
       <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
         <v>76</v>
-      </c>
-      <c r="C69" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -1927,7 +1813,7 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C71" t="s">
         <v>21</v>
@@ -1938,7 +1824,7 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
         <v>4</v>
@@ -1949,7 +1835,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
         <v>24</v>
@@ -1971,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75" t="s">
         <v>21</v>
@@ -1982,7 +1868,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C76" t="s">
         <v>22</v>
@@ -2026,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C81" t="s">
         <v>4</v>
@@ -2037,7 +1923,7 @@
         <v>3</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
         <v>25</v>
@@ -2048,7 +1934,7 @@
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
         <v>20</v>
@@ -2059,10 +1945,10 @@
         <v>5</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -2081,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
         <v>21</v>
@@ -2092,7 +1978,7 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
         <v>49</v>
@@ -2103,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s">
         <v>21</v>
@@ -2125,7 +2011,7 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
@@ -2136,7 +2022,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
         <v>25</v>
@@ -2147,7 +2033,7 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -2169,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C95" t="s">
         <v>1</v>
@@ -2180,7 +2066,7 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C96" t="s">
         <v>4</v>
@@ -2191,7 +2077,7 @@
         <v>3</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C97" t="s">
         <v>49</v>
@@ -2202,7 +2088,7 @@
         <v>4</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -2213,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C99" t="s">
         <v>21</v>
@@ -2224,7 +2110,7 @@
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -2246,7 +2132,7 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -2257,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C103" t="s">
         <v>1</v>
@@ -2268,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C104" t="s">
         <v>21</v>
@@ -2279,7 +2165,7 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C105" t="s">
         <v>22</v>
@@ -2301,7 +2187,7 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C107" t="s">
         <v>21</v>
@@ -2323,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C110" t="s">
         <v>19</v>
@@ -2334,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C111" t="s">
         <v>21</v>
@@ -2345,7 +2231,7 @@
         <v>3</v>
       </c>
       <c r="B112" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C112" t="s">
         <v>22</v>
@@ -2356,7 +2242,7 @@
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C113" t="s">
         <v>20</v>
@@ -2367,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C114" t="s">
         <v>21</v>
@@ -2378,10 +2264,10 @@
         <v>6</v>
       </c>
       <c r="B115" t="s">
+        <v>104</v>
+      </c>
+      <c r="C115" t="s">
         <v>105</v>
-      </c>
-      <c r="C115" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -2389,7 +2275,7 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
@@ -2400,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C117" t="s">
         <v>21</v>
@@ -2422,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C119" t="s">
         <v>20</v>
@@ -2444,10 +2330,10 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C121" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -2455,7 +2341,7 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C122" t="s">
         <v>4</v>
@@ -2466,7 +2352,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C123" t="s">
         <v>4</v>
@@ -2488,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C126" t="s">
         <v>19</v>
@@ -2499,7 +2385,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C127" t="s">
         <v>21</v>
@@ -2521,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C129" t="s">
         <v>24</v>
@@ -2532,10 +2418,10 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
+        <v>75</v>
+      </c>
+      <c r="C130" t="s">
         <v>76</v>
-      </c>
-      <c r="C130" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -2543,7 +2429,7 @@
         <v>6</v>
       </c>
       <c r="B131" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C131" t="s">
         <v>1</v>
@@ -2554,7 +2440,7 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C132" t="s">
         <v>4</v>
@@ -2565,7 +2451,7 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C133" t="s">
         <v>24</v>
@@ -2576,7 +2462,7 @@
         <v>9</v>
       </c>
       <c r="B134" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C134" t="s">
         <v>21</v>
@@ -2587,7 +2473,7 @@
         <v>10</v>
       </c>
       <c r="B135" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C135" t="s">
         <v>25</v>
@@ -2598,7 +2484,7 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C136" t="s">
         <v>23</v>
@@ -2609,7 +2495,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C137" t="s">
         <v>21</v>
@@ -2631,7 +2517,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C139" t="s">
         <v>24</v>
@@ -2653,7 +2539,7 @@
         <v>16</v>
       </c>
       <c r="B141" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C141" t="s">
         <v>48</v>
@@ -2664,7 +2550,7 @@
         <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C142" t="s">
         <v>48</v>
@@ -2675,7 +2561,7 @@
         <v>18</v>
       </c>
       <c r="B143" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C143" t="s">
         <v>22</v>
@@ -2697,7 +2583,7 @@
         <v>20</v>
       </c>
       <c r="B145" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C145" t="s">
         <v>21</v>
@@ -2719,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="B148" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C148" t="s">
         <v>1</v>
@@ -2730,7 +2616,10 @@
         <v>2</v>
       </c>
       <c r="B149" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+      <c r="C149" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -2738,7 +2627,10 @@
         <v>3</v>
       </c>
       <c r="B150" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+      <c r="C150" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -2746,6 +2638,9 @@
         <v>4</v>
       </c>
       <c r="B151" t="s">
+        <v>104</v>
+      </c>
+      <c r="C151" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2754,7 +2649,10 @@
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="C152" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -2762,7 +2660,7 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C153" t="s">
         <v>1</v>
@@ -2775,6 +2673,9 @@
       <c r="B154" t="s">
         <v>13</v>
       </c>
+      <c r="C154" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155">
@@ -2792,7 +2693,10 @@
         <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="C156" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -2800,7 +2704,10 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="C157" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -2808,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="B159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C159" t="s">
         <v>19</v>
@@ -2819,7 +2726,10 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>135</v>
+        <v>134</v>
+      </c>
+      <c r="C160" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -2827,7 +2737,10 @@
         <v>3</v>
       </c>
       <c r="B161" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="C161" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -2846,7 +2759,10 @@
         <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>137</v>
+        <v>136</v>
+      </c>
+      <c r="C163" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -2854,7 +2770,10 @@
         <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C164" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -2862,7 +2781,10 @@
         <v>7</v>
       </c>
       <c r="B165" t="s">
-        <v>138</v>
+        <v>137</v>
+      </c>
+      <c r="C165" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -2870,7 +2792,10 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>139</v>
+        <v>138</v>
+      </c>
+      <c r="C166" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -2878,7 +2803,10 @@
         <v>9</v>
       </c>
       <c r="B167" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="C167" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -2886,7 +2814,10 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="C168" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -2905,7 +2836,10 @@
         <v>2</v>
       </c>
       <c r="B171" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="C171" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -2915,13 +2849,19 @@
       <c r="B172" t="s">
         <v>33</v>
       </c>
+      <c r="C172" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>4</v>
       </c>
       <c r="B173" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="C173" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -2931,13 +2871,16 @@
       <c r="B174" t="s">
         <v>67</v>
       </c>
+      <c r="C174" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C175" t="s">
         <v>19</v>
@@ -2948,7 +2891,10 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+      <c r="C176" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -2956,7 +2902,10 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="C177" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -2975,7 +2924,10 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="C179" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -2994,7 +2946,10 @@
         <v>2</v>
       </c>
       <c r="B182" t="s">
-        <v>146</v>
+        <v>145</v>
+      </c>
+      <c r="C182" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -3002,7 +2957,7 @@
         <v>3</v>
       </c>
       <c r="B183" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C183" t="s">
         <v>19</v>
@@ -3013,7 +2968,10 @@
         <v>4</v>
       </c>
       <c r="B184" t="s">
-        <v>148</v>
+        <v>147</v>
+      </c>
+      <c r="C184" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
@@ -3021,7 +2979,10 @@
         <v>5</v>
       </c>
       <c r="B185" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="C185" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
@@ -3040,7 +3001,10 @@
         <v>7</v>
       </c>
       <c r="B187" t="s">
-        <v>149</v>
+        <v>148</v>
+      </c>
+      <c r="C187" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
@@ -3048,7 +3012,10 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C188" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
@@ -3056,7 +3023,7 @@
         <v>9</v>
       </c>
       <c r="B189" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C189" t="s">
         <v>1</v>
@@ -3067,7 +3034,10 @@
         <v>10</v>
       </c>
       <c r="B190" t="s">
-        <v>151</v>
+        <v>150</v>
+      </c>
+      <c r="C190" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -3075,7 +3045,10 @@
         <v>1</v>
       </c>
       <c r="B192" t="s">
-        <v>152</v>
+        <v>151</v>
+      </c>
+      <c r="C192" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -3083,7 +3056,10 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>116</v>
+        <v>115</v>
+      </c>
+      <c r="C193" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -3093,13 +3069,19 @@
       <c r="B194" t="s">
         <v>42</v>
       </c>
+      <c r="C194" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>4</v>
       </c>
       <c r="B195" t="s">
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="C195" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -3107,7 +3089,10 @@
         <v>5</v>
       </c>
       <c r="B196" t="s">
-        <v>142</v>
+        <v>141</v>
+      </c>
+      <c r="C196" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
@@ -3115,7 +3100,10 @@
         <v>6</v>
       </c>
       <c r="B197" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="C197" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
@@ -3123,7 +3111,10 @@
         <v>7</v>
       </c>
       <c r="B198" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="C198" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -3142,7 +3133,10 @@
         <v>9</v>
       </c>
       <c r="B200" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="C200" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
@@ -3150,7 +3144,10 @@
         <v>10</v>
       </c>
       <c r="B201" t="s">
-        <v>157</v>
+        <v>156</v>
+      </c>
+      <c r="C201" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -3169,7 +3166,10 @@
         <v>2</v>
       </c>
       <c r="B204" t="s">
-        <v>158</v>
+        <v>157</v>
+      </c>
+      <c r="C204" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -3177,7 +3177,10 @@
         <v>3</v>
       </c>
       <c r="B205" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="C205" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
@@ -3185,7 +3188,10 @@
         <v>4</v>
       </c>
       <c r="B206" t="s">
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="C206" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
@@ -3193,7 +3199,10 @@
         <v>5</v>
       </c>
       <c r="B207" t="s">
-        <v>160</v>
+        <v>159</v>
+      </c>
+      <c r="C207" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -3201,6 +3210,9 @@
         <v>6</v>
       </c>
       <c r="B208" t="s">
+        <v>104</v>
+      </c>
+      <c r="C208" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3209,7 +3221,10 @@
         <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="C209" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
@@ -3219,13 +3234,19 @@
       <c r="B210" t="s">
         <v>67</v>
       </c>
+      <c r="C210" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>9</v>
       </c>
       <c r="B211" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="C211" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
@@ -3233,7 +3254,10 @@
         <v>10</v>
       </c>
       <c r="B212" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="C212" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
@@ -3241,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="B214" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C214" t="s">
         <v>1</v>
@@ -3254,13 +3278,19 @@
       <c r="B215" t="s">
         <v>33</v>
       </c>
+      <c r="C215" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>3</v>
       </c>
       <c r="B216" t="s">
-        <v>163</v>
+        <v>162</v>
+      </c>
+      <c r="C216" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
@@ -3268,6 +3298,9 @@
         <v>4</v>
       </c>
       <c r="B217" t="s">
+        <v>75</v>
+      </c>
+      <c r="C217" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3276,7 +3309,7 @@
         <v>5</v>
       </c>
       <c r="B218" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C218" t="s">
         <v>19</v>
@@ -3287,7 +3320,10 @@
         <v>6</v>
       </c>
       <c r="B219" t="s">
-        <v>164</v>
+        <v>163</v>
+      </c>
+      <c r="C219" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
@@ -3295,7 +3331,10 @@
         <v>7</v>
       </c>
       <c r="B220" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C220" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
@@ -3314,7 +3353,10 @@
         <v>9</v>
       </c>
       <c r="B222" t="s">
-        <v>165</v>
+        <v>164</v>
+      </c>
+      <c r="C222" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
@@ -3322,7 +3364,10 @@
         <v>10</v>
       </c>
       <c r="B223" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="C223" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
@@ -3330,7 +3375,10 @@
         <v>11</v>
       </c>
       <c r="B224" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="C224" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
@@ -3340,13 +3388,19 @@
       <c r="B225" t="s">
         <v>67</v>
       </c>
+      <c r="C225" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>13</v>
       </c>
       <c r="B226" t="s">
-        <v>167</v>
+        <v>166</v>
+      </c>
+      <c r="C226" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
@@ -3365,7 +3419,10 @@
         <v>15</v>
       </c>
       <c r="B228" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="C228" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
@@ -3373,7 +3430,10 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C229" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
@@ -3381,7 +3441,7 @@
         <v>17</v>
       </c>
       <c r="B230" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C230" t="s">
         <v>1</v>
@@ -3392,7 +3452,10 @@
         <v>18</v>
       </c>
       <c r="B231" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="C231" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
@@ -3400,7 +3463,10 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>170</v>
+        <v>169</v>
+      </c>
+      <c r="C232" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
@@ -3408,7 +3474,10 @@
         <v>20</v>
       </c>
       <c r="B233" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C233" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
@@ -3427,7 +3496,10 @@
         <v>22</v>
       </c>
       <c r="B235" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="C235" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
@@ -3446,7 +3518,10 @@
         <v>2</v>
       </c>
       <c r="B238" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="C238" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
@@ -3454,7 +3529,7 @@
         <v>3</v>
       </c>
       <c r="B239" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C239" t="s">
         <v>1</v>
@@ -3465,7 +3540,10 @@
         <v>4</v>
       </c>
       <c r="B240" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="C240" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
@@ -3473,7 +3551,10 @@
         <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="C241" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
@@ -3492,7 +3573,10 @@
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>173</v>
+        <v>172</v>
+      </c>
+      <c r="C243" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
@@ -3500,7 +3584,10 @@
         <v>8</v>
       </c>
       <c r="B244" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="C244" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
@@ -3508,7 +3595,10 @@
         <v>9</v>
       </c>
       <c r="B245" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="C245" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
@@ -3527,7 +3617,10 @@
         <v>11</v>
       </c>
       <c r="B247" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+      <c r="C247" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
@@ -3535,7 +3628,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C248" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
@@ -3554,7 +3650,10 @@
         <v>14</v>
       </c>
       <c r="B250" t="s">
-        <v>177</v>
+        <v>176</v>
+      </c>
+      <c r="C250" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -3562,7 +3661,10 @@
         <v>15</v>
       </c>
       <c r="B251" t="s">
-        <v>178</v>
+        <v>177</v>
+      </c>
+      <c r="C251" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
@@ -3570,7 +3672,10 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="C252" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
@@ -3580,6 +3685,9 @@
       <c r="B253" t="s">
         <v>34</v>
       </c>
+      <c r="C253" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254">
@@ -3588,13 +3696,19 @@
       <c r="B254" s="1">
         <v>0.43</v>
       </c>
+      <c r="C254" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>19</v>
       </c>
       <c r="B255" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C255" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -3613,7 +3727,10 @@
         <v>21</v>
       </c>
       <c r="B257" t="s">
-        <v>179</v>
+        <v>178</v>
+      </c>
+      <c r="C257" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -3621,7 +3738,10 @@
         <v>22</v>
       </c>
       <c r="B258" t="s">
-        <v>180</v>
+        <v>179</v>
+      </c>
+      <c r="C258" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -3629,722 +3749,88 @@
         <v>1</v>
       </c>
       <c r="B260" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261">
+        <f>A260+1</f>
         <v>2</v>
       </c>
       <c r="B261" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262">
+        <f t="shared" ref="A262:A269" si="0">A261+1</f>
         <v>3</v>
       </c>
       <c r="B262" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B263" t="s">
-        <v>184</v>
+        <v>62</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B264" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B265" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B266" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B267" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B268" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>98</v>
-      </c>
-      <c r="C269" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A270">
-        <v>11</v>
-      </c>
-      <c r="B270" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A271">
-        <v>12</v>
-      </c>
-      <c r="B271" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A272">
-        <v>13</v>
-      </c>
-      <c r="B272" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A273">
-        <v>14</v>
-      </c>
-      <c r="B273" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A274">
-        <v>15</v>
-      </c>
-      <c r="B274" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A275">
-        <v>16</v>
-      </c>
-      <c r="B275" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A276">
-        <v>17</v>
-      </c>
-      <c r="B276" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A277">
-        <v>18</v>
-      </c>
-      <c r="B277" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A278">
-        <v>19</v>
-      </c>
-      <c r="B278" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A279">
-        <v>20</v>
-      </c>
-      <c r="B279" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A280">
-        <v>21</v>
-      </c>
-      <c r="B280" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A282">
-        <v>1</v>
-      </c>
-      <c r="B282" t="s">
-        <v>127</v>
-      </c>
-      <c r="C282" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A283">
-        <v>2</v>
-      </c>
-      <c r="B283" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A284">
-        <v>3</v>
-      </c>
-      <c r="B284" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A285">
-        <v>4</v>
-      </c>
-      <c r="B285" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A286">
-        <v>5</v>
-      </c>
-      <c r="B286" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A287">
-        <v>6</v>
-      </c>
-      <c r="B287" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A288">
-        <v>7</v>
-      </c>
-      <c r="B288" t="s">
-        <v>62</v>
-      </c>
-      <c r="C288" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A289">
-        <v>8</v>
-      </c>
-      <c r="B289" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A290">
-        <v>9</v>
-      </c>
-      <c r="B290" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A291">
-        <v>10</v>
-      </c>
-      <c r="B291" t="s">
-        <v>199</v>
-      </c>
-      <c r="C291" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A292">
-        <v>11</v>
-      </c>
-      <c r="B292" t="s">
-        <v>127</v>
-      </c>
-      <c r="C292" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A293">
-        <v>12</v>
-      </c>
-      <c r="B293" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A294">
-        <v>13</v>
-      </c>
-      <c r="B294" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A295">
-        <v>14</v>
-      </c>
-      <c r="B295" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A296">
-        <v>15</v>
-      </c>
-      <c r="B296" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A297">
-        <v>16</v>
-      </c>
-      <c r="B297" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A298">
-        <v>17</v>
-      </c>
-      <c r="B298" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A299">
-        <v>18</v>
-      </c>
-      <c r="B299" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A300">
-        <v>19</v>
-      </c>
-      <c r="B300" t="s">
-        <v>62</v>
-      </c>
-      <c r="C300" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A301">
-        <v>20</v>
-      </c>
-      <c r="B301" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A302">
-        <v>21</v>
-      </c>
-      <c r="B302" t="s">
-        <v>205</v>
-      </c>
-      <c r="C302" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A304">
-        <v>1</v>
-      </c>
-      <c r="B304" t="s">
-        <v>115</v>
-      </c>
-      <c r="C304" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A305">
-        <v>2</v>
-      </c>
-      <c r="B305" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A306">
-        <v>3</v>
-      </c>
-      <c r="B306" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A307">
-        <v>4</v>
-      </c>
-      <c r="B307" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A308">
-        <v>5</v>
-      </c>
-      <c r="B308" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A309">
-        <v>6</v>
-      </c>
-      <c r="B309" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A310">
-        <v>7</v>
-      </c>
-      <c r="B310" t="s">
-        <v>35</v>
-      </c>
-      <c r="C310" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A311">
-        <v>8</v>
-      </c>
-      <c r="B311" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A312">
-        <v>9</v>
-      </c>
-      <c r="B312" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A313">
-        <v>10</v>
-      </c>
-      <c r="B313" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A314">
-        <v>11</v>
-      </c>
-      <c r="B314" t="s">
-        <v>35</v>
-      </c>
-      <c r="C314" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A315">
-        <v>12</v>
-      </c>
-      <c r="B315" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A316">
-        <v>13</v>
-      </c>
-      <c r="B316" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A317">
-        <v>14</v>
-      </c>
-      <c r="B317" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A318">
-        <v>15</v>
-      </c>
-      <c r="B318" t="s">
-        <v>62</v>
-      </c>
-      <c r="C318" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A319">
-        <v>16</v>
-      </c>
-      <c r="B319" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A320">
-        <v>17</v>
-      </c>
-      <c r="B320" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A321">
-        <v>18</v>
-      </c>
-      <c r="B321" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A322">
-        <v>19</v>
-      </c>
-      <c r="B322" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A323">
-        <v>20</v>
-      </c>
-      <c r="B323" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A324">
-        <v>21</v>
-      </c>
-      <c r="B324" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A326">
-        <v>1</v>
-      </c>
-      <c r="B326" t="s">
-        <v>216</v>
-      </c>
-      <c r="C326" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A327">
-        <v>2</v>
-      </c>
-      <c r="B327" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A328">
-        <v>3</v>
-      </c>
-      <c r="B328" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A329">
-        <v>4</v>
-      </c>
-      <c r="B329" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A330">
-        <v>5</v>
-      </c>
-      <c r="B330" t="s">
-        <v>127</v>
-      </c>
-      <c r="C330" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A331">
-        <v>6</v>
-      </c>
-      <c r="B331" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A332">
-        <v>7</v>
-      </c>
-      <c r="B332" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A333">
-        <v>8</v>
-      </c>
-      <c r="B333" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A334">
-        <v>9</v>
-      </c>
-      <c r="B334" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A335">
-        <v>10</v>
-      </c>
-      <c r="B335" t="s">
-        <v>62</v>
-      </c>
-      <c r="C335" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A336">
-        <v>11</v>
-      </c>
-      <c r="B336" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A337">
-        <v>12</v>
-      </c>
-      <c r="B337" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A338">
-        <v>13</v>
-      </c>
-      <c r="B338" t="s">
-        <v>127</v>
-      </c>
-      <c r="C338" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A339">
-        <v>14</v>
-      </c>
-      <c r="B339" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A340">
-        <v>15</v>
-      </c>
-      <c r="B340" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A341">
-        <v>16</v>
-      </c>
-      <c r="B341" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A342">
-        <v>17</v>
-      </c>
-      <c r="B342" t="s">
-        <v>62</v>
-      </c>
-      <c r="C342" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A343">
-        <v>18</v>
-      </c>
-      <c r="B343" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A344">
-        <v>19</v>
-      </c>
-      <c r="B344" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A345">
-        <v>20</v>
-      </c>
-      <c r="B345" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A346">
-        <v>21</v>
-      </c>
-      <c r="B346" t="s">
-        <v>115</v>
-      </c>
-      <c r="C346" t="s">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/english.xlsx
+++ b/english.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamit\Desktop\LT\Computational Syntax\lab3\Universal-Dependencies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C779657-CD2C-40AD-8F43-47A38DD1CB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C395B69-A7F4-440F-B2E8-E1577B6DF64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{11BBC0D1-0CA4-4724-8D54-A31BE93C0D8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="176">
   <si>
     <t>Who</t>
   </si>
@@ -341,84 +341,18 @@
     <t>funds</t>
   </si>
   <si>
-    <t>discordance</t>
-  </si>
-  <si>
-    <t>between</t>
-  </si>
-  <si>
-    <t>economic</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>and</t>
   </si>
   <si>
     <t>CCONJ</t>
   </si>
   <si>
-    <t>political</t>
-  </si>
-  <si>
-    <t>rhetoric</t>
-  </si>
-  <si>
-    <t>familiar</t>
-  </si>
-  <si>
-    <t>or</t>
-  </si>
-  <si>
-    <t>should</t>
-  </si>
-  <si>
     <t>be</t>
   </si>
   <si>
-    <t>feasibility</t>
-  </si>
-  <si>
-    <t>estimates</t>
-  </si>
-  <si>
-    <t>it</t>
-  </si>
-  <si>
     <t>would</t>
   </si>
   <si>
-    <t>take</t>
-  </si>
-  <si>
-    <t>passengers</t>
-  </si>
-  <si>
-    <t>about</t>
-  </si>
-  <si>
-    <t>four</t>
-  </si>
-  <si>
-    <t>minutes</t>
-  </si>
-  <si>
-    <t>cross</t>
-  </si>
-  <si>
-    <t>Potomac</t>
-  </si>
-  <si>
-    <t>River</t>
-  </si>
-  <si>
-    <t>on</t>
-  </si>
-  <si>
-    <t>gondola</t>
-  </si>
-  <si>
     <t>he</t>
   </si>
   <si>
@@ -524,79 +458,115 @@
     <t>replaced</t>
   </si>
   <si>
-    <t>she</t>
-  </si>
-  <si>
-    <t>incensed</t>
-  </si>
-  <si>
-    <t>chit</t>
-  </si>
-  <si>
-    <t>girl</t>
-  </si>
-  <si>
-    <t>dare</t>
-  </si>
-  <si>
-    <t>make</t>
-  </si>
-  <si>
-    <t>fool</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>front</t>
-  </si>
-  <si>
-    <t>class</t>
-  </si>
-  <si>
-    <t>landslide</t>
-  </si>
-  <si>
-    <t>electoral</t>
-  </si>
-  <si>
-    <t>college</t>
-  </si>
-  <si>
-    <t>obscured</t>
-  </si>
-  <si>
-    <t>narrowness</t>
-  </si>
-  <si>
-    <t>victory</t>
-  </si>
-  <si>
-    <t>based</t>
-  </si>
-  <si>
-    <t>popular</t>
-  </si>
-  <si>
-    <t>vote</t>
-  </si>
-  <si>
-    <t>In</t>
-  </si>
-  <si>
-    <t>particular</t>
-  </si>
-  <si>
-    <t>computer</t>
-  </si>
-  <si>
-    <t>changed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">my </t>
-  </si>
-  <si>
-    <t>dramatically</t>
+    <t>aux</t>
+  </si>
+  <si>
+    <t>nmod : poss</t>
+  </si>
+  <si>
+    <t>obl</t>
+  </si>
+  <si>
+    <t>xcomp</t>
+  </si>
+  <si>
+    <t>obj</t>
+  </si>
+  <si>
+    <t>iobj</t>
+  </si>
+  <si>
+    <t>mark</t>
+  </si>
+  <si>
+    <t>ccomp</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>conj</t>
+  </si>
+  <si>
+    <t>UD</t>
+  </si>
+  <si>
+    <t>framework</t>
+  </si>
+  <si>
+    <t>consistent</t>
+  </si>
+  <si>
+    <t>annotation</t>
+  </si>
+  <si>
+    <t>grammar</t>
+  </si>
+  <si>
+    <t>across</t>
+  </si>
+  <si>
+    <t>different</t>
+  </si>
+  <si>
+    <t>human</t>
+  </si>
+  <si>
+    <t>languages</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>recognizes</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>She</t>
+  </si>
+  <si>
+    <t>made</t>
+  </si>
+  <si>
+    <t>him</t>
+  </si>
+  <si>
+    <t>cry</t>
+  </si>
+  <si>
+    <t>saw</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>telescope</t>
+  </si>
+  <si>
+    <t>Flying</t>
+  </si>
+  <si>
+    <t>planes</t>
+  </si>
+  <si>
+    <t>can</t>
+  </si>
+  <si>
+    <t>dangerous</t>
+  </si>
+  <si>
+    <t>acl</t>
+  </si>
+  <si>
+    <t>advcl</t>
   </si>
 </sst>
 </file>
@@ -632,9 +602,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F2D1FC-F999-4D45-A05E-3DEF813FC2A7}">
-  <dimension ref="A1:E269"/>
+  <dimension ref="A1:E227"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1356,6 +1325,12 @@
       <c r="C26" t="s">
         <v>48</v>
       </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -1366,6 +1341,12 @@
       </c>
       <c r="C27" t="s">
         <v>49</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1378,6 +1359,12 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
@@ -1389,6 +1376,12 @@
       <c r="C29" t="s">
         <v>21</v>
       </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
@@ -1399,6 +1392,12 @@
       </c>
       <c r="C30" t="s">
         <v>4</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1411,6 +1410,12 @@
       <c r="C31" t="s">
         <v>24</v>
       </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
@@ -1422,8 +1427,14 @@
       <c r="C32" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>8</v>
       </c>
@@ -1433,8 +1444,14 @@
       <c r="C33" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>9</v>
       </c>
@@ -1444,8 +1461,14 @@
       <c r="C34" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>10</v>
       </c>
@@ -1455,8 +1478,14 @@
       <c r="C35" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>11</v>
       </c>
@@ -1466,8 +1495,14 @@
       <c r="C36" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1</v>
       </c>
@@ -1477,8 +1512,14 @@
       <c r="C38" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2</v>
       </c>
@@ -1488,8 +1529,14 @@
       <c r="C39" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1499,8 +1546,14 @@
       <c r="C40" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>4</v>
       </c>
@@ -1510,8 +1563,14 @@
       <c r="C41" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>5</v>
       </c>
@@ -1521,8 +1580,14 @@
       <c r="C42" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>6</v>
       </c>
@@ -1532,8 +1597,14 @@
       <c r="C43" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>7</v>
       </c>
@@ -1543,8 +1614,14 @@
       <c r="C44" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>8</v>
       </c>
@@ -1554,8 +1631,14 @@
       <c r="C45" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>9</v>
       </c>
@@ -1565,8 +1648,14 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>10</v>
       </c>
@@ -1576,8 +1665,14 @@
       <c r="C47" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>11</v>
       </c>
@@ -1587,8 +1682,14 @@
       <c r="C48" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>12</v>
       </c>
@@ -1598,8 +1699,14 @@
       <c r="C49" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1</v>
       </c>
@@ -1609,8 +1716,14 @@
       <c r="C51" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2</v>
       </c>
@@ -1620,8 +1733,14 @@
       <c r="C52" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>3</v>
       </c>
@@ -1631,8 +1750,14 @@
       <c r="C53" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1642,8 +1767,14 @@
       <c r="C54" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>5</v>
       </c>
@@ -1653,8 +1784,14 @@
       <c r="C55" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55">
+        <v>8</v>
+      </c>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>6</v>
       </c>
@@ -1664,8 +1801,14 @@
       <c r="C56" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>7</v>
       </c>
@@ -1675,8 +1818,14 @@
       <c r="C57" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>8</v>
       </c>
@@ -1686,8 +1835,14 @@
       <c r="C58" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>9</v>
       </c>
@@ -1697,8 +1852,14 @@
       <c r="C59" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>10</v>
       </c>
@@ -1708,8 +1869,14 @@
       <c r="C60" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>11</v>
       </c>
@@ -1719,8 +1886,14 @@
       <c r="C61" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>12</v>
       </c>
@@ -1730,8 +1903,14 @@
       <c r="C62" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>13</v>
       </c>
@@ -1741,8 +1920,14 @@
       <c r="C63" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1</v>
       </c>
@@ -1752,8 +1937,14 @@
       <c r="C65" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2</v>
       </c>
@@ -1763,8 +1954,14 @@
       <c r="C66" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>3</v>
       </c>
@@ -1774,8 +1971,14 @@
       <c r="C67" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>4</v>
       </c>
@@ -1785,8 +1988,14 @@
       <c r="C68" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>5</v>
       </c>
@@ -1796,8 +2005,14 @@
       <c r="C69" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D69">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>6</v>
       </c>
@@ -1807,8 +2022,14 @@
       <c r="C70" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>7</v>
       </c>
@@ -1818,8 +2039,14 @@
       <c r="C71" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D71">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>8</v>
       </c>
@@ -1829,8 +2056,14 @@
       <c r="C72" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72">
+        <v>9</v>
+      </c>
+      <c r="E72" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>9</v>
       </c>
@@ -1840,8 +2073,14 @@
       <c r="C73" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>10</v>
       </c>
@@ -1851,8 +2090,14 @@
       <c r="C74" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D74">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>11</v>
       </c>
@@ -1862,8 +2107,14 @@
       <c r="C75" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D75">
+        <v>9</v>
+      </c>
+      <c r="E75" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>12</v>
       </c>
@@ -1873,8 +2124,14 @@
       <c r="C76" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D76">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>13</v>
       </c>
@@ -1884,8 +2141,14 @@
       <c r="C77" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D77">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>14</v>
       </c>
@@ -1895,8 +2158,14 @@
       <c r="C78" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1</v>
       </c>
@@ -1906,8 +2175,14 @@
       <c r="C80" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2</v>
       </c>
@@ -1915,10 +2190,16 @@
         <v>69</v>
       </c>
       <c r="C81" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="D81">
+        <v>4</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>3</v>
       </c>
@@ -1928,8 +2209,14 @@
       <c r="C82" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D82">
+        <v>4</v>
+      </c>
+      <c r="E82" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>4</v>
       </c>
@@ -1939,8 +2226,14 @@
       <c r="C83" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>5</v>
       </c>
@@ -1950,8 +2243,14 @@
       <c r="C84" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D84">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>6</v>
       </c>
@@ -1961,8 +2260,14 @@
       <c r="C85" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D85">
+        <v>7</v>
+      </c>
+      <c r="E85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>7</v>
       </c>
@@ -1972,8 +2277,14 @@
       <c r="C86" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D86">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>8</v>
       </c>
@@ -1983,8 +2294,14 @@
       <c r="C87" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D87">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>9</v>
       </c>
@@ -1994,8 +2311,14 @@
       <c r="C88" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D88">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>10</v>
       </c>
@@ -2005,8 +2328,14 @@
       <c r="C89" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D89">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>11</v>
       </c>
@@ -2016,8 +2345,14 @@
       <c r="C90" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D90">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>12</v>
       </c>
@@ -2027,8 +2362,14 @@
       <c r="C91" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D91">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>13</v>
       </c>
@@ -2038,8 +2379,14 @@
       <c r="C92" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D92">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>14</v>
       </c>
@@ -2049,8 +2396,14 @@
       <c r="C93" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>1</v>
       </c>
@@ -2060,8 +2413,14 @@
       <c r="C95" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D95">
+        <v>4</v>
+      </c>
+      <c r="E95" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2</v>
       </c>
@@ -2071,8 +2430,14 @@
       <c r="C96" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>3</v>
       </c>
@@ -2082,8 +2447,14 @@
       <c r="C97" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D97">
+        <v>4</v>
+      </c>
+      <c r="E97" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>4</v>
       </c>
@@ -2093,8 +2464,14 @@
       <c r="C98" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>5</v>
       </c>
@@ -2104,8 +2481,14 @@
       <c r="C99" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>6</v>
       </c>
@@ -2115,8 +2498,14 @@
       <c r="C100" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D100">
+        <v>5</v>
+      </c>
+      <c r="E100" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>7</v>
       </c>
@@ -2126,8 +2515,14 @@
       <c r="C101" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D101">
+        <v>8</v>
+      </c>
+      <c r="E101" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>8</v>
       </c>
@@ -2137,8 +2532,14 @@
       <c r="C102" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D102">
+        <v>6</v>
+      </c>
+      <c r="E102" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>9</v>
       </c>
@@ -2148,8 +2549,14 @@
       <c r="C103" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D103">
+        <v>10</v>
+      </c>
+      <c r="E103" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>10</v>
       </c>
@@ -2159,8 +2566,14 @@
       <c r="C104" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D104">
+        <v>8</v>
+      </c>
+      <c r="E104" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>11</v>
       </c>
@@ -2170,8 +2583,14 @@
       <c r="C105" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D105">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>12</v>
       </c>
@@ -2181,8 +2600,14 @@
       <c r="C106" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D106">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>13</v>
       </c>
@@ -2192,8 +2617,14 @@
       <c r="C107" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D107">
+        <v>8</v>
+      </c>
+      <c r="E107" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>14</v>
       </c>
@@ -2203,624 +2634,949 @@
       <c r="C108" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D108">
+        <v>4</v>
+      </c>
+      <c r="E108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+      <c r="E110" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>3</v>
       </c>
       <c r="B112" t="s">
+        <v>106</v>
+      </c>
+      <c r="C112" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+      <c r="E112" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>4</v>
+      </c>
+      <c r="B113" t="s">
+        <v>100</v>
+      </c>
+      <c r="C113" t="s">
         <v>101</v>
       </c>
-      <c r="C112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113">
-        <v>4</v>
-      </c>
-      <c r="B113" t="s">
-        <v>102</v>
-      </c>
-      <c r="C113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D113">
+        <v>5</v>
+      </c>
+      <c r="E113" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="D114">
+        <v>2</v>
+      </c>
+      <c r="E114" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>6</v>
       </c>
       <c r="B115" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="E115" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
+        <v>22</v>
+      </c>
+      <c r="D116">
+        <v>10</v>
+      </c>
+      <c r="E116" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
+        <v>62</v>
+      </c>
+      <c r="C117" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117">
+        <v>10</v>
+      </c>
+      <c r="E117" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>9</v>
+      </c>
+      <c r="B118" t="s">
+        <v>109</v>
+      </c>
+      <c r="C118" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>8</v>
-      </c>
-      <c r="B117" t="s">
-        <v>107</v>
-      </c>
-      <c r="C117" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>9</v>
-      </c>
-      <c r="B118" t="s">
-        <v>53</v>
-      </c>
-      <c r="C118" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D118">
+        <v>10</v>
+      </c>
+      <c r="E118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="D119">
+        <v>5</v>
+      </c>
+      <c r="E119" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C120" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121">
-        <v>12</v>
-      </c>
-      <c r="B121" t="s">
-        <v>109</v>
-      </c>
-      <c r="C121" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="E120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C122" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C123" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="D123">
+        <v>3</v>
+      </c>
+      <c r="E123" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B124" t="s">
+        <v>113</v>
+      </c>
+      <c r="C124" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>4</v>
+      </c>
+      <c r="B125" t="s">
+        <v>35</v>
+      </c>
+      <c r="C125" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125">
+        <v>5</v>
+      </c>
+      <c r="E125" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>114</v>
+      </c>
+      <c r="C126" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>6</v>
+      </c>
+      <c r="B127" t="s">
+        <v>71</v>
+      </c>
+      <c r="C127" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>7</v>
+      </c>
+      <c r="B128" t="s">
+        <v>115</v>
+      </c>
+      <c r="C128" t="s">
+        <v>23</v>
+      </c>
+      <c r="D128">
+        <v>8</v>
+      </c>
+      <c r="E128" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>8</v>
+      </c>
+      <c r="B129" t="s">
+        <v>116</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129">
+        <v>5</v>
+      </c>
+      <c r="E129" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>9</v>
+      </c>
+      <c r="B130" t="s">
+        <v>81</v>
+      </c>
+      <c r="C130" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130">
+        <v>10</v>
+      </c>
+      <c r="E130" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>10</v>
+      </c>
+      <c r="B131" t="s">
+        <v>117</v>
+      </c>
+      <c r="C131" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131">
+        <v>8</v>
+      </c>
+      <c r="E131" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>11</v>
+      </c>
+      <c r="B132" t="s">
         <v>18</v>
       </c>
-      <c r="C124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126">
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132">
+        <v>3</v>
+      </c>
+      <c r="E132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134">
         <v>1</v>
       </c>
-      <c r="B126" t="s">
-        <v>70</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B134" t="s">
+        <v>62</v>
+      </c>
+      <c r="C134" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127">
-        <v>2</v>
-      </c>
-      <c r="B127" t="s">
-        <v>112</v>
-      </c>
-      <c r="C127" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128">
-        <v>3</v>
-      </c>
-      <c r="B128" t="s">
-        <v>51</v>
-      </c>
-      <c r="C128" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129">
-        <v>4</v>
-      </c>
-      <c r="B129" t="s">
-        <v>113</v>
-      </c>
-      <c r="C129" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130">
-        <v>5</v>
-      </c>
-      <c r="B130" t="s">
-        <v>75</v>
-      </c>
-      <c r="C130" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131">
-        <v>6</v>
-      </c>
-      <c r="B131" t="s">
-        <v>114</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>7</v>
-      </c>
-      <c r="B132" t="s">
-        <v>115</v>
-      </c>
-      <c r="C132" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133">
-        <v>8</v>
-      </c>
-      <c r="B133" t="s">
-        <v>116</v>
-      </c>
-      <c r="C133" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134">
-        <v>9</v>
-      </c>
-      <c r="B134" t="s">
-        <v>117</v>
-      </c>
-      <c r="C134" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
         <v>118</v>
       </c>
       <c r="C135" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="D135">
+        <v>4</v>
+      </c>
+      <c r="E135" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B136" t="s">
+        <v>33</v>
+      </c>
+      <c r="C136" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136">
+        <v>4</v>
+      </c>
+      <c r="E136" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>4</v>
+      </c>
+      <c r="B137" t="s">
         <v>119</v>
       </c>
-      <c r="C136" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137">
-        <v>12</v>
-      </c>
-      <c r="B137" t="s">
-        <v>120</v>
-      </c>
       <c r="C137" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B138" t="s">
         <v>67</v>
       </c>
       <c r="C138" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="D138">
+        <v>7</v>
+      </c>
+      <c r="E138" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B139" t="s">
+        <v>120</v>
+      </c>
+      <c r="C139" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139">
+        <v>7</v>
+      </c>
+      <c r="E139" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
         <v>121</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140">
+        <v>4</v>
+      </c>
+      <c r="E140" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
+        <v>81</v>
+      </c>
+      <c r="C141" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141">
+        <v>10</v>
+      </c>
+      <c r="E141" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>9</v>
+      </c>
+      <c r="B142" t="s">
+        <v>62</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142">
+        <v>10</v>
+      </c>
+      <c r="E142" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>10</v>
+      </c>
+      <c r="B143" t="s">
+        <v>122</v>
+      </c>
+      <c r="C143" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143">
+        <v>7</v>
+      </c>
+      <c r="E143" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>11</v>
+      </c>
+      <c r="B144" t="s">
+        <v>18</v>
+      </c>
+      <c r="C144" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144">
+        <v>4</v>
+      </c>
+      <c r="E144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>32</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>2</v>
+      </c>
+      <c r="B147" t="s">
+        <v>123</v>
+      </c>
+      <c r="C147" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>3</v>
+      </c>
+      <c r="B148" t="s">
+        <v>124</v>
+      </c>
+      <c r="C148" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148">
+        <v>4</v>
+      </c>
+      <c r="E148" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>4</v>
+      </c>
+      <c r="B149" t="s">
+        <v>125</v>
+      </c>
+      <c r="C149" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149">
+        <v>2</v>
+      </c>
+      <c r="E149" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>5</v>
+      </c>
+      <c r="B150" t="s">
+        <v>81</v>
+      </c>
+      <c r="C150" t="s">
+        <v>22</v>
+      </c>
+      <c r="D150">
+        <v>7</v>
+      </c>
+      <c r="E150" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>6</v>
+      </c>
+      <c r="B151" t="s">
         <v>62</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C151" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>16</v>
-      </c>
-      <c r="B141" t="s">
-        <v>122</v>
-      </c>
-      <c r="C141" t="s">
+      <c r="D151">
+        <v>7</v>
+      </c>
+      <c r="E151" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>7</v>
+      </c>
+      <c r="B152" t="s">
+        <v>126</v>
+      </c>
+      <c r="C152" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>71</v>
+      </c>
+      <c r="C153" t="s">
+        <v>22</v>
+      </c>
+      <c r="D153">
+        <v>10</v>
+      </c>
+      <c r="E153" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>9</v>
+      </c>
+      <c r="B154" t="s">
+        <v>127</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>10</v>
+      </c>
+      <c r="E154" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>10</v>
+      </c>
+      <c r="B155" t="s">
+        <v>128</v>
+      </c>
+      <c r="C155" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155">
+        <v>7</v>
+      </c>
+      <c r="E155" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>11</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+      <c r="E156" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>129</v>
+      </c>
+      <c r="C158" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142">
-        <v>17</v>
-      </c>
-      <c r="B142" t="s">
-        <v>123</v>
-      </c>
-      <c r="C142" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143">
-        <v>18</v>
-      </c>
-      <c r="B143" t="s">
-        <v>124</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="D158">
+        <v>5</v>
+      </c>
+      <c r="E158" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>2</v>
+      </c>
+      <c r="B159" t="s">
+        <v>103</v>
+      </c>
+      <c r="C159" t="s">
+        <v>4</v>
+      </c>
+      <c r="D159">
+        <v>5</v>
+      </c>
+      <c r="E159" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>3</v>
+      </c>
+      <c r="B160" t="s">
+        <v>42</v>
+      </c>
+      <c r="C160" t="s">
+        <v>4</v>
+      </c>
+      <c r="D160">
+        <v>5</v>
+      </c>
+      <c r="E160" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s">
+        <v>130</v>
+      </c>
+      <c r="C161" t="s">
+        <v>4</v>
+      </c>
+      <c r="D161">
+        <v>5</v>
+      </c>
+      <c r="E161" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>5</v>
+      </c>
+      <c r="B162" t="s">
+        <v>119</v>
+      </c>
+      <c r="C162" t="s">
+        <v>24</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>6</v>
+      </c>
+      <c r="B163" t="s">
+        <v>131</v>
+      </c>
+      <c r="C163" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144">
-        <v>19</v>
-      </c>
-      <c r="B144" t="s">
-        <v>62</v>
-      </c>
-      <c r="C144" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145">
-        <v>20</v>
-      </c>
-      <c r="B145" t="s">
-        <v>125</v>
-      </c>
-      <c r="C145" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146">
-        <v>21</v>
-      </c>
-      <c r="B146" t="s">
-        <v>18</v>
-      </c>
-      <c r="C146" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148">
-        <v>1</v>
-      </c>
-      <c r="B148" t="s">
-        <v>126</v>
-      </c>
-      <c r="C148" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149">
-        <v>2</v>
-      </c>
-      <c r="B149" t="s">
-        <v>127</v>
-      </c>
-      <c r="C149" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150">
-        <v>3</v>
-      </c>
-      <c r="B150" t="s">
-        <v>128</v>
-      </c>
-      <c r="C150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151">
-        <v>4</v>
-      </c>
-      <c r="B151" t="s">
-        <v>104</v>
-      </c>
-      <c r="C151" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152">
-        <v>5</v>
-      </c>
-      <c r="B152" t="s">
-        <v>129</v>
-      </c>
-      <c r="C152" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153">
-        <v>6</v>
-      </c>
-      <c r="B153" t="s">
-        <v>130</v>
-      </c>
-      <c r="C153" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154">
+      <c r="D163">
+        <v>9</v>
+      </c>
+      <c r="E163" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A164">
         <v>7</v>
       </c>
-      <c r="B154" t="s">
-        <v>13</v>
-      </c>
-      <c r="C154" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155">
-        <v>8</v>
-      </c>
-      <c r="B155" t="s">
-        <v>62</v>
-      </c>
-      <c r="C155" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156">
-        <v>9</v>
-      </c>
-      <c r="B156" t="s">
-        <v>131</v>
-      </c>
-      <c r="C156" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157">
-        <v>10</v>
-      </c>
-      <c r="B157" t="s">
+      <c r="B164" t="s">
         <v>132</v>
-      </c>
-      <c r="C157" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159">
-        <v>1</v>
-      </c>
-      <c r="B159" t="s">
-        <v>133</v>
-      </c>
-      <c r="C159" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160">
-        <v>2</v>
-      </c>
-      <c r="B160" t="s">
-        <v>134</v>
-      </c>
-      <c r="C160" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161">
-        <v>3</v>
-      </c>
-      <c r="B161" t="s">
-        <v>135</v>
-      </c>
-      <c r="C161" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162">
-        <v>4</v>
-      </c>
-      <c r="B162" t="s">
-        <v>35</v>
-      </c>
-      <c r="C162" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A163">
-        <v>5</v>
-      </c>
-      <c r="B163" t="s">
-        <v>136</v>
-      </c>
-      <c r="C163" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164">
-        <v>6</v>
-      </c>
-      <c r="B164" t="s">
-        <v>71</v>
       </c>
       <c r="C164" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D164">
+        <v>9</v>
+      </c>
+      <c r="E164" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="C165" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="D165">
+        <v>9</v>
+      </c>
+      <c r="E165" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B166" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C166" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D166">
+        <v>5</v>
+      </c>
+      <c r="E166" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="C167" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="D167">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B168" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="D168">
+        <v>5</v>
+      </c>
+      <c r="E168" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>1</v>
       </c>
@@ -2830,1007 +3586,895 @@
       <c r="C170" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D170">
+        <v>2</v>
+      </c>
+      <c r="E170" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>2</v>
       </c>
       <c r="B171" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C171" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D171">
+        <v>4</v>
+      </c>
+      <c r="E171" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>3</v>
       </c>
       <c r="B172" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C172" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D172">
+        <v>4</v>
+      </c>
+      <c r="E172" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>4</v>
       </c>
       <c r="B173" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C173" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>5</v>
       </c>
       <c r="B174" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="C174" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="C175" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+      <c r="D175">
+        <v>7</v>
+      </c>
+      <c r="E175" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="C176" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="D176">
+        <v>4</v>
+      </c>
+      <c r="E176" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C177" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="D177">
+        <v>10</v>
+      </c>
+      <c r="E177" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>9</v>
       </c>
       <c r="B178" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C178" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="D178">
+        <v>10</v>
+      </c>
+      <c r="E178" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C179" t="s">
+        <v>24</v>
+      </c>
+      <c r="D179">
+        <v>7</v>
+      </c>
+      <c r="E179" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>11</v>
+      </c>
+      <c r="B180" t="s">
+        <v>18</v>
+      </c>
+      <c r="C180" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180">
+        <v>4</v>
+      </c>
+      <c r="E180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>1</v>
+      </c>
+      <c r="B182" t="s">
+        <v>149</v>
+      </c>
+      <c r="C182" t="s">
+        <v>48</v>
+      </c>
+      <c r="D182">
+        <v>4</v>
+      </c>
+      <c r="E182" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>2</v>
+      </c>
+      <c r="B183" t="s">
+        <v>53</v>
+      </c>
+      <c r="C183" t="s">
+        <v>4</v>
+      </c>
+      <c r="D183">
+        <v>4</v>
+      </c>
+      <c r="E183" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>3</v>
+      </c>
+      <c r="B184" t="s">
+        <v>35</v>
+      </c>
+      <c r="C184" t="s">
+        <v>19</v>
+      </c>
+      <c r="D184">
+        <v>4</v>
+      </c>
+      <c r="E184" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>4</v>
+      </c>
+      <c r="B185" t="s">
+        <v>150</v>
+      </c>
+      <c r="C185" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181">
-        <v>1</v>
-      </c>
-      <c r="B181" t="s">
-        <v>32</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182">
-        <v>2</v>
-      </c>
-      <c r="B182" t="s">
-        <v>145</v>
-      </c>
-      <c r="C182" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183">
-        <v>3</v>
-      </c>
-      <c r="B183" t="s">
-        <v>146</v>
-      </c>
-      <c r="C183" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184">
-        <v>4</v>
-      </c>
-      <c r="B184" t="s">
-        <v>147</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>5</v>
+      </c>
+      <c r="B186" t="s">
+        <v>44</v>
+      </c>
+      <c r="C186" t="s">
+        <v>22</v>
+      </c>
+      <c r="D186">
+        <v>7</v>
+      </c>
+      <c r="E186" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>6</v>
+      </c>
+      <c r="B187" t="s">
+        <v>151</v>
+      </c>
+      <c r="C187" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187">
+        <v>7</v>
+      </c>
+      <c r="E187" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>7</v>
+      </c>
+      <c r="B188" t="s">
+        <v>152</v>
+      </c>
+      <c r="C188" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185">
-        <v>5</v>
-      </c>
-      <c r="B185" t="s">
-        <v>81</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="D188">
+        <v>4</v>
+      </c>
+      <c r="E188" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>71</v>
+      </c>
+      <c r="C189" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186">
-        <v>6</v>
-      </c>
-      <c r="B186" t="s">
-        <v>62</v>
-      </c>
-      <c r="C186" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187">
-        <v>7</v>
-      </c>
-      <c r="B187" t="s">
-        <v>148</v>
-      </c>
-      <c r="C187" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188">
-        <v>8</v>
-      </c>
-      <c r="B188" t="s">
-        <v>71</v>
-      </c>
-      <c r="C188" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189">
-        <v>9</v>
-      </c>
-      <c r="B189" t="s">
-        <v>149</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D189">
+        <v>9</v>
+      </c>
+      <c r="E189" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B190" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C190" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D190">
+        <v>7</v>
+      </c>
+      <c r="E190" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>10</v>
+      </c>
+      <c r="B191" t="s">
+        <v>154</v>
+      </c>
+      <c r="C191" t="s">
+        <v>22</v>
+      </c>
+      <c r="D191">
+        <v>13</v>
+      </c>
+      <c r="E191" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192">
+        <v>11</v>
+      </c>
+      <c r="B192" t="s">
+        <v>155</v>
+      </c>
+      <c r="C192" t="s">
+        <v>20</v>
+      </c>
+      <c r="D192">
+        <v>13</v>
+      </c>
+      <c r="E192" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>12</v>
+      </c>
+      <c r="B193" t="s">
+        <v>156</v>
+      </c>
+      <c r="C193" t="s">
+        <v>20</v>
+      </c>
+      <c r="D193">
+        <v>13</v>
+      </c>
+      <c r="E193" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>13</v>
+      </c>
+      <c r="B194" t="s">
+        <v>157</v>
+      </c>
+      <c r="C194" t="s">
+        <v>21</v>
+      </c>
+      <c r="D194">
+        <v>7</v>
+      </c>
+      <c r="E194" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>14</v>
+      </c>
+      <c r="B195" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195">
+        <v>4</v>
+      </c>
+      <c r="E195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A197">
         <v>1</v>
       </c>
-      <c r="B192" t="s">
-        <v>151</v>
-      </c>
-      <c r="C192" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193">
-        <v>2</v>
-      </c>
-      <c r="B193" t="s">
-        <v>115</v>
-      </c>
-      <c r="C193" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194">
+      <c r="B197" t="s">
+        <v>62</v>
+      </c>
+      <c r="C197" t="s">
+        <v>19</v>
+      </c>
+      <c r="D197">
+        <v>2</v>
+      </c>
+      <c r="E197" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>2</v>
+      </c>
+      <c r="B198" t="s">
+        <v>158</v>
+      </c>
+      <c r="C198" t="s">
+        <v>21</v>
+      </c>
+      <c r="D198">
         <v>3</v>
       </c>
-      <c r="B194" t="s">
-        <v>42</v>
-      </c>
-      <c r="C194" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195">
-        <v>4</v>
-      </c>
-      <c r="B195" t="s">
-        <v>152</v>
-      </c>
-      <c r="C195" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196">
-        <v>5</v>
-      </c>
-      <c r="B196" t="s">
-        <v>141</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="E198" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>3</v>
+      </c>
+      <c r="B199" t="s">
+        <v>159</v>
+      </c>
+      <c r="C199" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197">
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>4</v>
+      </c>
+      <c r="B200" t="s">
+        <v>75</v>
+      </c>
+      <c r="C200" t="s">
+        <v>76</v>
+      </c>
+      <c r="D200">
+        <v>9</v>
+      </c>
+      <c r="E200" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <v>5</v>
+      </c>
+      <c r="B201" t="s">
+        <v>35</v>
+      </c>
+      <c r="C201" t="s">
+        <v>19</v>
+      </c>
+      <c r="D201">
+        <v>7</v>
+      </c>
+      <c r="E201" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A202">
         <v>6</v>
       </c>
-      <c r="B197" t="s">
-        <v>153</v>
-      </c>
-      <c r="C197" t="s">
+      <c r="B202" t="s">
+        <v>160</v>
+      </c>
+      <c r="C202" t="s">
+        <v>20</v>
+      </c>
+      <c r="D202">
+        <v>7</v>
+      </c>
+      <c r="E202" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <v>7</v>
+      </c>
+      <c r="B203" t="s">
+        <v>161</v>
+      </c>
+      <c r="C203" t="s">
+        <v>21</v>
+      </c>
+      <c r="D203">
+        <v>9</v>
+      </c>
+      <c r="E203" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <v>8</v>
+      </c>
+      <c r="B204" t="s">
+        <v>53</v>
+      </c>
+      <c r="C204" t="s">
+        <v>4</v>
+      </c>
+      <c r="D204">
+        <v>9</v>
+      </c>
+      <c r="E204" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <v>9</v>
+      </c>
+      <c r="B205" t="s">
+        <v>162</v>
+      </c>
+      <c r="C205" t="s">
+        <v>25</v>
+      </c>
+      <c r="D205">
+        <v>3</v>
+      </c>
+      <c r="E205" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A207">
+        <v>1</v>
+      </c>
+      <c r="B207" t="s">
+        <v>163</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+      <c r="E207" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A208">
+        <v>2</v>
+      </c>
+      <c r="B208" t="s">
+        <v>164</v>
+      </c>
+      <c r="C208" t="s">
+        <v>24</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A209">
+        <v>3</v>
+      </c>
+      <c r="B209" t="s">
+        <v>165</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1</v>
+      </c>
+      <c r="D209">
+        <v>2</v>
+      </c>
+      <c r="E209" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>4</v>
+      </c>
+      <c r="B210" t="s">
+        <v>166</v>
+      </c>
+      <c r="C210" t="s">
+        <v>24</v>
+      </c>
+      <c r="D210">
+        <v>2</v>
+      </c>
+      <c r="E210" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>5</v>
+      </c>
+      <c r="B211" t="s">
+        <v>18</v>
+      </c>
+      <c r="C211" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211">
+        <v>2</v>
+      </c>
+      <c r="E211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A213">
+        <v>1</v>
+      </c>
+      <c r="B213" t="s">
+        <v>32</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1</v>
+      </c>
+      <c r="D213">
+        <v>2</v>
+      </c>
+      <c r="E213" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <v>2</v>
+      </c>
+      <c r="B214" t="s">
+        <v>167</v>
+      </c>
+      <c r="C214" t="s">
+        <v>24</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <v>3</v>
+      </c>
+      <c r="B215" t="s">
+        <v>62</v>
+      </c>
+      <c r="C215" t="s">
+        <v>19</v>
+      </c>
+      <c r="D215">
+        <v>4</v>
+      </c>
+      <c r="E215" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>4</v>
+      </c>
+      <c r="B216" t="s">
+        <v>168</v>
+      </c>
+      <c r="C216" t="s">
+        <v>21</v>
+      </c>
+      <c r="D216">
+        <v>2</v>
+      </c>
+      <c r="E216" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>5</v>
+      </c>
+      <c r="B217" t="s">
+        <v>13</v>
+      </c>
+      <c r="C217" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198">
-        <v>7</v>
-      </c>
-      <c r="B198" t="s">
-        <v>154</v>
-      </c>
-      <c r="C198" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199">
-        <v>8</v>
-      </c>
-      <c r="B199" t="s">
+      <c r="D217">
+        <v>4</v>
+      </c>
+      <c r="E217" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>6</v>
+      </c>
+      <c r="B218" t="s">
         <v>62</v>
-      </c>
-      <c r="C199" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200">
-        <v>9</v>
-      </c>
-      <c r="B200" t="s">
-        <v>155</v>
-      </c>
-      <c r="C200" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201">
-        <v>10</v>
-      </c>
-      <c r="B201" t="s">
-        <v>156</v>
-      </c>
-      <c r="C201" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203">
-        <v>1</v>
-      </c>
-      <c r="B203" t="s">
-        <v>62</v>
-      </c>
-      <c r="C203" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204">
-        <v>2</v>
-      </c>
-      <c r="B204" t="s">
-        <v>157</v>
-      </c>
-      <c r="C204" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205">
-        <v>3</v>
-      </c>
-      <c r="B205" t="s">
-        <v>78</v>
-      </c>
-      <c r="C205" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206">
-        <v>4</v>
-      </c>
-      <c r="B206" t="s">
-        <v>158</v>
-      </c>
-      <c r="C206" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207">
-        <v>5</v>
-      </c>
-      <c r="B207" t="s">
-        <v>159</v>
-      </c>
-      <c r="C207" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208">
-        <v>6</v>
-      </c>
-      <c r="B208" t="s">
-        <v>104</v>
-      </c>
-      <c r="C208" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A209">
-        <v>7</v>
-      </c>
-      <c r="B209" t="s">
-        <v>78</v>
-      </c>
-      <c r="C209" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210">
-        <v>8</v>
-      </c>
-      <c r="B210" t="s">
-        <v>67</v>
-      </c>
-      <c r="C210" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A211">
-        <v>9</v>
-      </c>
-      <c r="B211" t="s">
-        <v>111</v>
-      </c>
-      <c r="C211" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212">
-        <v>10</v>
-      </c>
-      <c r="B212" t="s">
-        <v>160</v>
-      </c>
-      <c r="C212" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214">
-        <v>1</v>
-      </c>
-      <c r="B214" t="s">
-        <v>161</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A215">
-        <v>2</v>
-      </c>
-      <c r="B215" t="s">
-        <v>33</v>
-      </c>
-      <c r="C215" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216">
-        <v>3</v>
-      </c>
-      <c r="B216" t="s">
-        <v>162</v>
-      </c>
-      <c r="C216" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A217">
-        <v>4</v>
-      </c>
-      <c r="B217" t="s">
-        <v>75</v>
-      </c>
-      <c r="C217" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218">
-        <v>5</v>
-      </c>
-      <c r="B218" t="s">
-        <v>133</v>
       </c>
       <c r="C218" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D218">
+        <v>7</v>
+      </c>
+      <c r="E218" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B219" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C219" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D219">
+        <v>4</v>
+      </c>
+      <c r="E219" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B220" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="C220" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A221">
-        <v>8</v>
-      </c>
-      <c r="B221" t="s">
-        <v>35</v>
-      </c>
-      <c r="C221" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="D220">
+        <v>2</v>
+      </c>
+      <c r="E220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B222" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C222" t="s">
+        <v>24</v>
+      </c>
+      <c r="D222">
+        <v>2</v>
+      </c>
+      <c r="E222" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>2</v>
+      </c>
+      <c r="B223" t="s">
+        <v>171</v>
+      </c>
+      <c r="C223" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A223">
-        <v>10</v>
-      </c>
-      <c r="B223" t="s">
-        <v>110</v>
-      </c>
-      <c r="C223" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D223">
+        <v>5</v>
+      </c>
+      <c r="E223" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B224" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C224" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="D224">
+        <v>5</v>
+      </c>
+      <c r="E224" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B225" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C225" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+      <c r="E225" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B226" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C226" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B227" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C227" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A228">
-        <v>15</v>
-      </c>
-      <c r="B228" t="s">
-        <v>167</v>
-      </c>
-      <c r="C228" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229">
-        <v>16</v>
-      </c>
-      <c r="B229" t="s">
-        <v>71</v>
-      </c>
-      <c r="C229" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A230">
-        <v>17</v>
-      </c>
-      <c r="B230" t="s">
-        <v>168</v>
-      </c>
-      <c r="C230" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231">
-        <v>18</v>
-      </c>
-      <c r="B231" t="s">
-        <v>81</v>
-      </c>
-      <c r="C231" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A232">
-        <v>19</v>
-      </c>
-      <c r="B232" t="s">
-        <v>169</v>
-      </c>
-      <c r="C232" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A233">
-        <v>20</v>
-      </c>
-      <c r="B233" t="s">
-        <v>71</v>
-      </c>
-      <c r="C233" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A234">
-        <v>21</v>
-      </c>
-      <c r="B234" t="s">
-        <v>62</v>
-      </c>
-      <c r="C234" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A235">
-        <v>22</v>
-      </c>
-      <c r="B235" t="s">
-        <v>170</v>
-      </c>
-      <c r="C235" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A237">
-        <v>1</v>
-      </c>
-      <c r="B237" t="s">
-        <v>62</v>
-      </c>
-      <c r="C237" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A238">
-        <v>2</v>
-      </c>
-      <c r="B238" t="s">
-        <v>171</v>
-      </c>
-      <c r="C238" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A239">
-        <v>3</v>
-      </c>
-      <c r="B239" t="s">
-        <v>126</v>
-      </c>
-      <c r="C239" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A240">
-        <v>4</v>
-      </c>
-      <c r="B240" t="s">
-        <v>78</v>
-      </c>
-      <c r="C240" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A241">
-        <v>5</v>
-      </c>
-      <c r="B241" t="s">
-        <v>81</v>
-      </c>
-      <c r="C241" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A242">
-        <v>6</v>
-      </c>
-      <c r="B242" t="s">
-        <v>62</v>
-      </c>
-      <c r="C242" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A243">
-        <v>7</v>
-      </c>
-      <c r="B243" t="s">
-        <v>172</v>
-      </c>
-      <c r="C243" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A244">
-        <v>8</v>
-      </c>
-      <c r="B244" t="s">
-        <v>173</v>
-      </c>
-      <c r="C244" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A245">
-        <v>9</v>
-      </c>
-      <c r="B245" t="s">
-        <v>174</v>
-      </c>
-      <c r="C245" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A246">
-        <v>10</v>
-      </c>
-      <c r="B246" t="s">
-        <v>62</v>
-      </c>
-      <c r="C246" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A247">
-        <v>11</v>
-      </c>
-      <c r="B247" t="s">
-        <v>175</v>
-      </c>
-      <c r="C247" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A248">
-        <v>12</v>
-      </c>
-      <c r="B248" t="s">
-        <v>71</v>
-      </c>
-      <c r="C248" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A249">
-        <v>13</v>
-      </c>
-      <c r="B249" t="s">
-        <v>35</v>
-      </c>
-      <c r="C249" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A250">
-        <v>14</v>
-      </c>
-      <c r="B250" t="s">
-        <v>176</v>
-      </c>
-      <c r="C250" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A251">
-        <v>15</v>
-      </c>
-      <c r="B251" t="s">
-        <v>177</v>
-      </c>
-      <c r="C251" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A252">
-        <v>16</v>
-      </c>
-      <c r="B252" t="s">
-        <v>124</v>
-      </c>
-      <c r="C252" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A253">
-        <v>17</v>
-      </c>
-      <c r="B253" t="s">
-        <v>34</v>
-      </c>
-      <c r="C253" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A254">
-        <v>18</v>
-      </c>
-      <c r="B254" s="1">
-        <v>0.43</v>
-      </c>
-      <c r="C254" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A255">
-        <v>19</v>
-      </c>
-      <c r="B255" t="s">
-        <v>71</v>
-      </c>
-      <c r="C255" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A256">
-        <v>20</v>
-      </c>
-      <c r="B256" t="s">
-        <v>62</v>
-      </c>
-      <c r="C256" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A257">
-        <v>21</v>
-      </c>
-      <c r="B257" t="s">
-        <v>178</v>
-      </c>
-      <c r="C257" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A258">
-        <v>22</v>
-      </c>
-      <c r="B258" t="s">
-        <v>179</v>
-      </c>
-      <c r="C258" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A260">
-        <v>1</v>
-      </c>
-      <c r="B260" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A261">
-        <f>A260+1</f>
-        <v>2</v>
-      </c>
-      <c r="B261" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A262">
-        <f t="shared" ref="A262:A269" si="0">A261+1</f>
-        <v>3</v>
-      </c>
-      <c r="B262" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A263">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B263" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A264">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B264" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A265">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B265" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A266">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B266" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A267">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B267" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A268">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B268" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A269">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B269" t="s">
-        <v>185</v>
+        <v>8</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+      <c r="E227" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
